--- a/exports/trend_1d/OFSS_full_report.xlsx
+++ b/exports/trend_1d/OFSS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.12</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42087</v>
+        <v>42088</v>
       </c>
       <c r="H2" t="n">
-        <v>2787.5</v>
+        <v>2773</v>
       </c>
       <c r="I2" t="n">
         <v>2781.955179191948</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.49</v>
+        <v>-5.98</v>
       </c>
       <c r="L2" t="n">
         <v>6.26</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>7.05</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42104</v>
+        <v>42107</v>
       </c>
       <c r="H3" t="n">
-        <v>2932</v>
+        <v>3008</v>
       </c>
       <c r="I3" t="n">
         <v>2968.444755890455</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.73</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>7.3</v>
+        <v>11.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="N3" t="n">
         <v>4.33</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.37</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>2838</v>
+        <v>2767</v>
       </c>
       <c r="I4" t="n">
         <v>2786.369935152472</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.65</v>
+        <v>-8.01</v>
       </c>
       <c r="L4" t="n">
-        <v>6.28</v>
+        <v>9.31</v>
       </c>
       <c r="M4" t="n">
         <v>0.73</v>
       </c>
       <c r="N4" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
         <v>2.59</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.69</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42137</v>
+        <v>42138</v>
       </c>
       <c r="H5" t="n">
-        <v>3051.5</v>
+        <v>3087.5</v>
       </c>
       <c r="I5" t="n">
         <v>3054.313853814048</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.28</v>
+        <v>-11.58</v>
       </c>
       <c r="L5" t="n">
         <v>13.03</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.24</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42249</v>
+        <v>42250</v>
       </c>
       <c r="H6" t="n">
-        <v>3604.5</v>
+        <v>3464.5</v>
       </c>
       <c r="I6" t="n">
         <v>3562.62296627255</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K6" t="n">
-        <v>16.74</v>
+        <v>12.21</v>
       </c>
       <c r="L6" t="n">
         <v>3.22</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.94</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42450</v>
+        <v>42451</v>
       </c>
       <c r="H7" t="n">
-        <v>3058</v>
+        <v>3076.5</v>
       </c>
       <c r="I7" t="n">
         <v>3065.023315283408</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K7" t="n">
-        <v>11.73</v>
+        <v>11.2</v>
       </c>
       <c r="L7" t="n">
         <v>4.56</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42510</v>
+        <v>42513</v>
       </c>
       <c r="H8" t="n">
-        <v>2989.5</v>
+        <v>2964.5</v>
       </c>
       <c r="I8" t="n">
         <v>2967.494956403564</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.83</v>
+        <v>-3.64</v>
       </c>
       <c r="L8" t="n">
-        <v>3.49</v>
+        <v>3.97</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.25</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42569</v>
+        <v>42570</v>
       </c>
       <c r="H9" t="n">
-        <v>3135.5</v>
+        <v>3147.5</v>
       </c>
       <c r="I9" t="n">
         <v>3144.043767779207</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.77</v>
+        <v>-6.17</v>
       </c>
       <c r="L9" t="n">
         <v>7.71</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>6.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42612</v>
+        <v>42613</v>
       </c>
       <c r="H10" t="n">
-        <v>3049</v>
+        <v>3029.5</v>
       </c>
       <c r="I10" t="n">
         <v>3045.310780898595</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.13</v>
+        <v>-3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>3.61</v>
+        <v>4.24</v>
       </c>
       <c r="M10" t="n">
         <v>2.74</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12.63</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42712</v>
+        <v>42713</v>
       </c>
       <c r="H11" t="n">
-        <v>2713</v>
+        <v>2751.5</v>
       </c>
       <c r="I11" t="n">
         <v>2721.562560600277</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>10.45</v>
+        <v>9.18</v>
       </c>
       <c r="L11" t="n">
         <v>5.97</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.58</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42843</v>
+        <v>42844</v>
       </c>
       <c r="H12" t="n">
-        <v>3323.5</v>
+        <v>3124</v>
       </c>
       <c r="I12" t="n">
         <v>3215.517602415931</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K12" t="n">
-        <v>20.79</v>
+        <v>13.54</v>
       </c>
       <c r="L12" t="n">
         <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>1.14</v>
+        <v>4.83</v>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>1.42</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42870</v>
+        <v>42871</v>
       </c>
       <c r="H13" t="n">
-        <v>3300.5</v>
+        <v>3428.5</v>
       </c>
       <c r="I13" t="n">
         <v>3367.344343099286</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.65</v>
+        <v>-9.75</v>
       </c>
       <c r="L13" t="n">
-        <v>7.35</v>
+        <v>10.31</v>
       </c>
       <c r="M13" t="n">
         <v>1.44</v>
       </c>
       <c r="N13" t="n">
-        <v>2.24</v>
+        <v>3.88</v>
       </c>
       <c r="O13" t="n">
         <v>-6</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>7.96</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H14" t="n">
-        <v>3167.5</v>
+        <v>3119</v>
       </c>
       <c r="I14" t="n">
         <v>3155.552482392221</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.61</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>8.98</v>
+        <v>9.48</v>
       </c>
       <c r="M14" t="n">
         <v>0.82</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43006</v>
+        <v>43007</v>
       </c>
       <c r="H15" t="n">
-        <v>3158.5</v>
+        <v>3198</v>
       </c>
       <c r="I15" t="n">
         <v>3184.752022918397</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.27</v>
+        <v>-2.53</v>
       </c>
       <c r="L15" t="n">
         <v>6.91</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.26</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43157</v>
+        <v>43158</v>
       </c>
       <c r="H16" t="n">
-        <v>3543</v>
+        <v>3420.5</v>
       </c>
       <c r="I16" t="n">
         <v>3492.125939260844</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K16" t="n">
-        <v>10.79</v>
+        <v>6.96</v>
       </c>
       <c r="L16" t="n">
         <v>5.14</v>
@@ -1353,7 +1544,7 @@
         <v>2.48</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>3.46</v>
       </c>
       <c r="O16" t="n">
         <v>1.25</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>10.19</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H17" t="n">
-        <v>3483.5</v>
+        <v>3570.5</v>
       </c>
       <c r="I17" t="n">
         <v>3555.361567593501</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.84</v>
+        <v>-4.39</v>
       </c>
       <c r="L17" t="n">
-        <v>4.65</v>
+        <v>5.23</v>
       </c>
       <c r="M17" t="n">
         <v>1.23</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>9.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H18" t="n">
-        <v>3529.5</v>
+        <v>3412</v>
       </c>
       <c r="I18" t="n">
         <v>3501.234007109808</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.15</v>
+        <v>-4.44</v>
       </c>
       <c r="L18" t="n">
-        <v>4.66</v>
+        <v>4.76</v>
       </c>
       <c r="M18" t="n">
         <v>1.01</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>12.76</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43265</v>
+        <v>43266</v>
       </c>
       <c r="H19" t="n">
-        <v>3550</v>
+        <v>3643</v>
       </c>
       <c r="I19" t="n">
         <v>3621.994653075485</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.04</v>
+        <v>-6.77</v>
       </c>
       <c r="L19" t="n">
-        <v>6.65</v>
+        <v>7.85</v>
       </c>
       <c r="M19" t="n">
         <v>1.23</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.13</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H20" t="n">
-        <v>3649</v>
+        <v>3496</v>
       </c>
       <c r="I20" t="n">
         <v>3496.560984972059</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K20" t="n">
-        <v>0.16</v>
+        <v>-4.04</v>
       </c>
       <c r="L20" t="n">
         <v>9.24</v>
@@ -1581,7 +1820,7 @@
         <v>2.66</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>4.19</v>
       </c>
       <c r="O20" t="n">
         <v>2.62</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43357</v>
+        <v>43360</v>
       </c>
       <c r="H21" t="n">
-        <v>3779.5</v>
+        <v>4003</v>
       </c>
       <c r="I21" t="n">
         <v>3803.943102172633</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.109999999999999</v>
+        <v>-14.5</v>
       </c>
       <c r="L21" t="n">
-        <v>10.47</v>
+        <v>19.05</v>
       </c>
       <c r="M21" t="n">
         <v>0.23</v>
       </c>
       <c r="N21" t="n">
-        <v>2.52</v>
+        <v>5.91</v>
       </c>
       <c r="O21" t="n">
         <v>-4.19</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>10.5</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H22" t="n">
-        <v>3642</v>
+        <v>3552.5</v>
       </c>
       <c r="I22" t="n">
         <v>3582.838228961502</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.02</v>
+        <v>-11.25</v>
       </c>
       <c r="L22" t="n">
-        <v>9.74</v>
+        <v>12.49</v>
       </c>
       <c r="M22" t="n">
         <v>0.05</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15.25</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43465</v>
+        <v>43466</v>
       </c>
       <c r="H23" t="n">
-        <v>3266.5</v>
+        <v>3287</v>
       </c>
       <c r="I23" t="n">
         <v>3274.062819214099</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K23" t="n">
-        <v>8.050000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="L23" t="n">
         <v>4.66</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.01</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43511</v>
+        <v>43514</v>
       </c>
       <c r="H24" t="n">
-        <v>3196</v>
+        <v>3104</v>
       </c>
       <c r="I24" t="n">
         <v>3184.794730060713</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.77</v>
+        <v>-5.57</v>
       </c>
       <c r="L24" t="n">
         <v>7.41</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.73</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43567</v>
+        <v>43570</v>
       </c>
       <c r="H25" t="n">
-        <v>3121</v>
+        <v>3174.5</v>
       </c>
       <c r="I25" t="n">
         <v>3138.071485107976</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.55</v>
+        <v>-2.27</v>
       </c>
       <c r="L25" t="n">
         <v>3.37</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43620</v>
+        <v>43622</v>
       </c>
       <c r="H26" t="n">
-        <v>2955.5</v>
+        <v>2919</v>
       </c>
       <c r="I26" t="n">
         <v>2948.245437386301</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.9</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>7.54</v>
+        <v>8.32</v>
       </c>
       <c r="M26" t="n">
         <v>0.73</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.47</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43658</v>
+        <v>43661</v>
       </c>
       <c r="H27" t="n">
-        <v>2875</v>
+        <v>2959</v>
       </c>
       <c r="I27" t="n">
         <v>2912.367498020712</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K27" t="n">
-        <v>1.51</v>
+        <v>-1.37</v>
       </c>
       <c r="L27" t="n">
         <v>2.76</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>11.32</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43686</v>
+        <v>43690</v>
       </c>
       <c r="H28" t="n">
-        <v>2743.5</v>
+        <v>2660.5</v>
       </c>
       <c r="I28" t="n">
         <v>2667.284092942903</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.28</v>
+        <v>-10.09</v>
       </c>
       <c r="L28" t="n">
-        <v>7.77</v>
+        <v>10.87</v>
       </c>
       <c r="M28" t="n">
         <v>1.19</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>12.67</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H29" t="n">
-        <v>2545</v>
+        <v>2758</v>
       </c>
       <c r="I29" t="n">
         <v>2727.22730140363</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K29" t="n">
-        <v>4.34</v>
+        <v>-3.66</v>
       </c>
       <c r="L29" t="n">
-        <v>4.06</v>
+        <v>4.79</v>
       </c>
       <c r="M29" t="n">
         <v>0.87</v>
       </c>
       <c r="N29" t="n">
-        <v>4.02</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="O29" t="n">
         <v>-3.03</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>16.17</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43790</v>
+        <v>43791</v>
       </c>
       <c r="H30" t="n">
-        <v>2567</v>
+        <v>2515.5</v>
       </c>
       <c r="I30" t="n">
         <v>2555.045803884738</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.93</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>9.77</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.59</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43840</v>
+        <v>43843</v>
       </c>
       <c r="H31" t="n">
-        <v>2463</v>
+        <v>2557.5</v>
       </c>
       <c r="I31" t="n">
         <v>2495.011386347275</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K31" t="n">
-        <v>2.09</v>
+        <v>-1.67</v>
       </c>
       <c r="L31" t="n">
-        <v>4.29</v>
+        <v>4.85</v>
       </c>
       <c r="M31" t="n">
         <v>1.03</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.55</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H32" t="n">
-        <v>2397.5</v>
+        <v>2356.5</v>
       </c>
       <c r="I32" t="n">
         <v>2364.13354459233</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.26</v>
+        <v>-7.86</v>
       </c>
       <c r="L32" t="n">
         <v>8.99</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.28</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43928</v>
+        <v>43929</v>
       </c>
       <c r="H33" t="n">
-        <v>1731.5</v>
+        <v>1748.5</v>
       </c>
       <c r="I33" t="n">
         <v>1739.718219010738</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K33" t="n">
-        <v>26.52</v>
+        <v>25.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.91</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>27.15</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44158</v>
+        <v>44159</v>
       </c>
       <c r="H34" t="n">
-        <v>2625</v>
+        <v>2616</v>
       </c>
       <c r="I34" t="n">
         <v>2617.856596355246</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K34" t="n">
-        <v>50.13</v>
+        <v>49.61</v>
       </c>
       <c r="L34" t="n">
         <v>6.72</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>159</v>
+        <v>160</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>7.9</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44188</v>
+        <v>44189</v>
       </c>
       <c r="H35" t="n">
-        <v>2735.5</v>
+        <v>2807</v>
       </c>
       <c r="I35" t="n">
         <v>2786.405115939938</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.57</v>
+        <v>-7.3</v>
       </c>
       <c r="L35" t="n">
-        <v>6.48</v>
+        <v>9.17</v>
       </c>
       <c r="M35" t="n">
         <v>1.28</v>
       </c>
       <c r="N35" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="O35" t="n">
         <v>-0.34</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>7.91</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44236</v>
+        <v>44237</v>
       </c>
       <c r="H36" t="n">
-        <v>2817.5</v>
+        <v>2786</v>
       </c>
       <c r="I36" t="n">
         <v>2793.747678171407</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="n">
-        <v>0.37</v>
+        <v>-0.75</v>
       </c>
       <c r="L36" t="n">
         <v>2.32</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>9.51</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44258</v>
+        <v>44259</v>
       </c>
       <c r="H37" t="n">
-        <v>2815</v>
+        <v>2837.5</v>
       </c>
       <c r="I37" t="n">
         <v>2836.353368754484</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.04</v>
+        <v>-1.85</v>
       </c>
       <c r="L37" t="n">
         <v>4.47</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.06</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H38" t="n">
-        <v>4058.5</v>
+        <v>3966.5</v>
       </c>
       <c r="I38" t="n">
         <v>3991.707902939796</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K38" t="n">
-        <v>43.03</v>
+        <v>39.79</v>
       </c>
       <c r="L38" t="n">
         <v>7.63</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>8</v>
+      </c>
+      <c r="U38" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.61</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H39" t="n">
-        <v>3153</v>
+        <v>3230</v>
       </c>
       <c r="I39" t="n">
         <v>3223.869817225375</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K39" t="n">
-        <v>20.51</v>
+        <v>18.57</v>
       </c>
       <c r="L39" t="n">
         <v>6.25</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>7</v>
+      </c>
+      <c r="U39" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H40" t="n">
-        <v>3074</v>
+        <v>3006</v>
       </c>
       <c r="I40" t="n">
         <v>3044.318059553733</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.83</v>
+        <v>-6.93</v>
       </c>
       <c r="L40" t="n">
-        <v>7.52</v>
+        <v>7.88</v>
       </c>
       <c r="M40" t="n">
         <v>2.04</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44774</v>
+        <v>44775</v>
       </c>
       <c r="H41" t="n">
-        <v>2751</v>
+        <v>2879</v>
       </c>
       <c r="I41" t="n">
         <v>2856.336654879509</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K41" t="n">
-        <v>8.48</v>
+        <v>4.22</v>
       </c>
       <c r="L41" t="n">
         <v>6.82</v>
@@ -2778,7 +3269,7 @@
         <v>1.86</v>
       </c>
       <c r="N41" t="n">
-        <v>4.43</v>
+        <v>4.65</v>
       </c>
       <c r="O41" t="n">
         <v>-2.21</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>10.2</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44803</v>
+        <v>44805</v>
       </c>
       <c r="H42" t="n">
-        <v>2760</v>
+        <v>2697.5</v>
       </c>
       <c r="I42" t="n">
         <v>2719.993911483231</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.13</v>
+        <v>-6.3</v>
       </c>
       <c r="L42" t="n">
-        <v>5.12</v>
+        <v>6.51</v>
       </c>
       <c r="M42" t="n">
         <v>1.35</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.08</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44875</v>
+        <v>44876</v>
       </c>
       <c r="H43" t="n">
-        <v>2634</v>
+        <v>2675</v>
       </c>
       <c r="I43" t="n">
         <v>2638.840677900313</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K43" t="n">
-        <v>2.35</v>
+        <v>0.83</v>
       </c>
       <c r="L43" t="n">
         <v>4.71</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>4.64</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H44" t="n">
-        <v>2640</v>
+        <v>2617.5</v>
       </c>
       <c r="I44" t="n">
         <v>2634.611729707624</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.31</v>
+        <v>-2.15</v>
       </c>
       <c r="L44" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="M44" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="N44" t="n">
         <v>1.8</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>6.49</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44942</v>
+        <v>44943</v>
       </c>
       <c r="H45" t="n">
-        <v>2688.5</v>
+        <v>2722.5</v>
       </c>
       <c r="I45" t="n">
         <v>2710.283815430084</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.71</v>
+        <v>-4.01</v>
       </c>
       <c r="L45" t="n">
         <v>4.72</v>
@@ -3006,7 +3545,7 @@
         <v>0.87</v>
       </c>
       <c r="N45" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="O45" t="n">
         <v>-0.85</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>5.68</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45054</v>
+        <v>45055</v>
       </c>
       <c r="H46" t="n">
-        <v>3266.5</v>
+        <v>3011.5</v>
       </c>
       <c r="I46" t="n">
         <v>3076.171561807371</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K46" t="n">
-        <v>19.98</v>
+        <v>10.62</v>
       </c>
       <c r="L46" t="n">
         <v>4.1</v>
       </c>
       <c r="M46" t="n">
-        <v>1.18</v>
+        <v>7.94</v>
       </c>
       <c r="N46" t="n">
-        <v>1.98</v>
+        <v>7.81</v>
       </c>
       <c r="O46" t="n">
         <v>1.26</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>9.01</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45089</v>
+        <v>45090</v>
       </c>
       <c r="H47" t="n">
-        <v>3161</v>
+        <v>3351</v>
       </c>
       <c r="I47" t="n">
         <v>3275.818534936029</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.96</v>
+        <v>-11.27</v>
       </c>
       <c r="L47" t="n">
-        <v>6.89</v>
+        <v>12.6</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
       </c>
       <c r="N47" t="n">
-        <v>1.76</v>
+        <v>6.01</v>
       </c>
       <c r="O47" t="n">
         <v>-7.81</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.9</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45191</v>
+        <v>45194</v>
       </c>
       <c r="H48" t="n">
-        <v>3726</v>
+        <v>3667.5</v>
       </c>
       <c r="I48" t="n">
         <v>3691.348561655594</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K48" t="n">
-        <v>11.19</v>
+        <v>9.44</v>
       </c>
       <c r="L48" t="n">
         <v>5.18</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>8.82</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45246</v>
+        <v>45247</v>
       </c>
       <c r="H49" t="n">
-        <v>3673.5</v>
+        <v>3711</v>
       </c>
       <c r="I49" t="n">
         <v>3699.658283914903</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.16</v>
+        <v>-1.19</v>
       </c>
       <c r="L49" t="n">
         <v>3.34</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.2</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45397</v>
+        <v>45398</v>
       </c>
       <c r="H50" t="n">
-        <v>7363.5</v>
+        <v>7176.5</v>
       </c>
       <c r="I50" t="n">
         <v>7315.16248374788</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K50" t="n">
-        <v>98.42</v>
+        <v>93.38</v>
       </c>
       <c r="L50" t="n">
         <v>5.63</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.16</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45448</v>
+        <v>45449</v>
       </c>
       <c r="H51" t="n">
-        <v>7280.5</v>
+        <v>7697.5</v>
       </c>
       <c r="I51" t="n">
         <v>7456.099108288183</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.45</v>
+        <v>-7.26</v>
       </c>
       <c r="L51" t="n">
-        <v>4.79</v>
+        <v>7.62</v>
       </c>
       <c r="M51" t="n">
         <v>1.37</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>11.98</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H52" t="n">
-        <v>9786.5</v>
+        <v>9309</v>
       </c>
       <c r="I52" t="n">
         <v>9481.11963085722</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>27.14</v>
+        <v>20.94</v>
       </c>
       <c r="L52" t="n">
         <v>5.25</v>
       </c>
       <c r="M52" t="n">
-        <v>2.78</v>
+        <v>4.61</v>
       </c>
       <c r="N52" t="n">
-        <v>4.78</v>
+        <v>4.88</v>
       </c>
       <c r="O52" t="n">
         <v>5.73</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>13.64</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45537</v>
+        <v>45538</v>
       </c>
       <c r="H53" t="n">
-        <v>10303</v>
+        <v>10790.5</v>
       </c>
       <c r="I53" t="n">
         <v>10579.18671340272</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K53" t="n">
-        <v>-10.68</v>
+        <v>-15.91</v>
       </c>
       <c r="L53" t="n">
-        <v>14.42</v>
+        <v>17.12</v>
       </c>
       <c r="M53" t="n">
         <v>2.65</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>11.16</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45553</v>
+        <v>45554</v>
       </c>
       <c r="H54" t="n">
-        <v>10606</v>
+        <v>10403</v>
       </c>
       <c r="I54" t="n">
         <v>10575.34450624789</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.71</v>
+        <v>-3.59</v>
       </c>
       <c r="L54" t="n">
-        <v>6.08</v>
+        <v>7.02</v>
       </c>
       <c r="M54" t="n">
         <v>0.93</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>14.69</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H55" t="n">
-        <v>11017.5</v>
+        <v>11554.5</v>
       </c>
       <c r="I55" t="n">
         <v>11404.11286679085</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.91</v>
+        <v>-11.07</v>
       </c>
       <c r="L55" t="n">
-        <v>9.94</v>
+        <v>11.36</v>
       </c>
       <c r="M55" t="n">
         <v>2.56</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>12.4</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H56" t="n">
-        <v>11046.5</v>
+        <v>10786.5</v>
       </c>
       <c r="I56" t="n">
         <v>10931.43256369553</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.4</v>
+        <v>-6.65</v>
       </c>
       <c r="L56" t="n">
-        <v>5.78</v>
+        <v>7.04</v>
       </c>
       <c r="M56" t="n">
         <v>3.46</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>12.81</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H57" t="n">
-        <v>7488.5</v>
+        <v>7660.5</v>
       </c>
       <c r="I57" t="n">
         <v>7597.564552009631</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K57" t="n">
-        <v>30.58</v>
+        <v>28.98</v>
       </c>
       <c r="L57" t="n">
         <v>3.82</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.01</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="H58" t="n">
-        <v>8689.5</v>
+        <v>8532.5</v>
       </c>
       <c r="I58" t="n">
         <v>8660.014717567368</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K58" t="n">
-        <v>13.43</v>
+        <v>11.38</v>
       </c>
       <c r="L58" t="n">
         <v>2.12</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>7.48</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="H59" t="n">
-        <v>8178.5</v>
+        <v>9006.5</v>
       </c>
       <c r="I59" t="n">
         <v>8637.144737391092</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K59" t="n">
-        <v>4.15</v>
+        <v>-5.56</v>
       </c>
       <c r="L59" t="n">
-        <v>2.94</v>
+        <v>5.97</v>
       </c>
       <c r="M59" t="n">
-        <v>1.92</v>
+        <v>5.95</v>
       </c>
       <c r="N59" t="n">
-        <v>2.28</v>
+        <v>10.12</v>
       </c>
       <c r="O59" t="n">
         <v>-1.81</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>10.64</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H60" t="n">
-        <v>8661</v>
+        <v>8278</v>
       </c>
       <c r="I60" t="n">
         <v>8283.939887797704</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.84</v>
+        <v>-8.09</v>
       </c>
       <c r="L60" t="n">
-        <v>4.8</v>
+        <v>8.25</v>
       </c>
       <c r="M60" t="n">
         <v>1.31</v>
       </c>
       <c r="N60" t="n">
-        <v>1.73</v>
+        <v>4.42</v>
       </c>
       <c r="O60" t="n">
         <v>10.12</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>11.21</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="H61" t="n">
-        <v>8840</v>
+        <v>9072.5</v>
       </c>
       <c r="I61" t="n">
         <v>8882.284537749298</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>-6.79</v>
+        <v>-9.6</v>
       </c>
       <c r="L61" t="n">
-        <v>6.99</v>
+        <v>9.98</v>
       </c>
       <c r="M61" t="n">
         <v>0.65</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>9.56</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H62" t="n">
-        <v>8380.5</v>
+        <v>8294.5</v>
       </c>
       <c r="I62" t="n">
         <v>8302.621215326579</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K62" t="n">
-        <v>-7.63</v>
+        <v>-8.58</v>
       </c>
       <c r="L62" t="n">
-        <v>8.380000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M62" t="n">
         <v>0.67</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.81</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="H63" t="n">
-        <v>7783</v>
+        <v>7789.5</v>
       </c>
       <c r="I63" t="n">
         <v>7785.365063131864</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K63" t="n">
-        <v>6.17</v>
+        <v>6.09</v>
       </c>
       <c r="L63" t="n">
         <v>2.44</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.58</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="H64" t="n">
-        <v>7243</v>
+        <v>7061.5</v>
       </c>
       <c r="I64" t="n">
         <v>7198.925363366068</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.02</v>
+        <v>-9.35</v>
       </c>
       <c r="L64" t="n">
-        <v>7.52</v>
+        <v>10.83</v>
       </c>
       <c r="M64" t="n">
         <v>1.74</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>9.43</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="H65" t="n">
-        <v>6415</v>
+        <v>6753.5</v>
       </c>
       <c r="I65" t="n">
         <v>6731.6187318443</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K65" t="n">
-        <v>9.16</v>
+        <v>4.36</v>
       </c>
       <c r="L65" t="n">
         <v>1.88</v>
       </c>
       <c r="M65" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>4.64</v>
+        <v>5.28</v>
       </c>
       <c r="O65" t="n">
         <v>-2.51</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.56</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H66" t="n">
-        <v>9470</v>
+        <v>9265.5</v>
       </c>
       <c r="I66" t="n">
         <v>9269.501338275459</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K66" t="n">
-        <v>40.22</v>
+        <v>37.2</v>
       </c>
       <c r="L66" t="n">
         <v>3.83</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>11.52</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="H67" t="n">
-        <v>9862.5</v>
+        <v>10468.5</v>
       </c>
       <c r="I67" t="n">
         <v>10283.44799294523</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.44</v>
+        <v>-12.98</v>
       </c>
       <c r="L67" t="n">
-        <v>7.12</v>
+        <v>13.43</v>
       </c>
       <c r="M67" t="n">
         <v>1.85</v>
       </c>
       <c r="N67" t="n">
-        <v>2.54</v>
+        <v>6.14</v>
       </c>
       <c r="O67" t="n">
         <v>-2.16</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>12.54</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="H68" t="n">
-        <v>10843</v>
+        <v>10652</v>
       </c>
       <c r="I68" t="n">
         <v>10710.36721444457</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K68" t="n">
-        <v>3.58</v>
+        <v>1.75</v>
       </c>
       <c r="L68" t="n">
         <v>5.67</v>
       </c>
       <c r="M68" t="n">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="N68" t="n">
         <v>6.71</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>14.71</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H69" t="n">
-        <v>12190</v>
+        <v>12540</v>
       </c>
       <c r="I69" t="n">
         <v>12219.42692818836</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K69" t="n">
-        <v>-14.44</v>
+        <v>-17.72</v>
       </c>
       <c r="L69" t="n">
-        <v>15.24</v>
+        <v>17.72</v>
       </c>
       <c r="M69" t="n">
         <v>1.01</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>10.23</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="H70" t="n">
-        <v>11896</v>
+        <v>10911</v>
       </c>
       <c r="I70" t="n">
         <v>11257.19848289247</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K70" t="n">
-        <v>-5.14</v>
+        <v>-12.99</v>
       </c>
       <c r="L70" t="n">
-        <v>9.44</v>
+        <v>13.08</v>
       </c>
       <c r="M70" t="n">
         <v>1.52</v>
       </c>
       <c r="N70" t="n">
-        <v>2.81</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="O70" t="n">
         <v>2.87</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>26</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.2</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127.6</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="11">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.27</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.17</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.29</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>98.42</v>
+        <v>93.38</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.6</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.07</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.78</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.24</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="25">
@@ -9649,7 +10508,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.22</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="26">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.92</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="27">
@@ -9669,7 +10528,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.19</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="28">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
